--- a/basedatos_partidas/salida/descompuestos/CT-18-01-040.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-18-01-040.xlsx
@@ -539,10 +539,10 @@
         <v>0.125</v>
       </c>
       <c r="G10" t="n">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="H10" t="n">
-        <v>15.62</v>
+        <v>14.75</v>
       </c>
     </row>
     <row r="11">
@@ -565,10 +565,10 @@
         <v>1.08</v>
       </c>
       <c r="G11" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="H11" t="n">
-        <v>4.54</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="12">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>22.88</v>
+        <v>22.44</v>
       </c>
     </row>
     <row r="16">
@@ -828,7 +828,7 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>29.05</v>
+        <v>28.61</v>
       </c>
       <c r="H25" t="n">
         <v>0.29</v>
@@ -847,7 +847,7 @@
       </c>
       <c r="G26" s="4" t="n"/>
       <c r="H26" s="5" t="n">
-        <v>29.34</v>
+        <v>28.9</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-18-01-040.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-18-01-040.xlsx
@@ -591,10 +591,10 @@
         <v>0.35</v>
       </c>
       <c r="G12" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="H12" t="n">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="13">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>22.44</v>
+        <v>22.37</v>
       </c>
     </row>
     <row r="16">
@@ -828,7 +828,7 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>28.61</v>
+        <v>28.54</v>
       </c>
       <c r="H25" t="n">
         <v>0.29</v>
@@ -847,7 +847,7 @@
       </c>
       <c r="G26" s="4" t="n"/>
       <c r="H26" s="5" t="n">
-        <v>28.9</v>
+        <v>28.83</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-18-01-040.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-18-01-040.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H26"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 18 Obras exteriores y urbanismo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Pavimentos exteriores</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
